--- a/成績管理sys_テスト仕様書.xlsx
+++ b/成績管理sys_テスト仕様書.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20357"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFB72FE2-4581-402A-8C52-26578D3DA527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri_sys\seiseki_manage_sys\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F5B7AC-99FE-494E-8752-88B71F8BE144}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="専攻情報管理機能" sheetId="5" r:id="rId1"/>
@@ -19,23 +24,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="218">
   <si>
     <t>機能名</t>
   </si>
@@ -127,9 +121,6 @@
 専攻情報管理へ</t>
   </si>
   <si>
-    <t>専攻詳細表示機能</t>
-  </si>
-  <si>
     <t>url: 'localhost:8080/manager/major?id=4' (対象idパラメーターつき)</t>
   </si>
   <si>
@@ -223,12 +214,6 @@
 一番右端の列の各詳細ボタンが、表示/動作している</t>
   </si>
   <si>
-    <t>教科詳細表示機能</t>
-  </si>
-  <si>
-    <t>url: 'localhost:8080/manager/subject?id=4' (対象idパラメーターつき)</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 ログイン表示へ
 教科詳細表示へ</t>
@@ -319,9 +304,6 @@
 一番右端の列の各詳細ボタンが、表示/動作している</t>
   </si>
   <si>
-    <t>クラス詳細表示機能</t>
-  </si>
-  <si>
     <t>url: 'localhost:8080/manager/class?id=4' (対象idパラメーターつき)</t>
   </si>
   <si>
@@ -498,12 +480,915 @@
   <si>
     <t>ログイン表示がでるか？</t>
   </si>
+  <si>
+    <t>専攻詳細表示機能
+専攻削除機能</t>
+    <rPh sb="9" eb="11">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科詳細表示機能
+教科削除機能</t>
+    <rPh sb="9" eb="11">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>サクジョキノウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス詳細表示機能
+クラス削除機能</t>
+    <rPh sb="13" eb="15">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科登録表示機能</t>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>url: 'localhost:8080/manager/subject_register'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ログイン表示へ
+教科登録表示へ</t>
+    <rPh sb="12" eb="14">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ログイン表示へ
+教科登録表示へ</t>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+教科登録表示ができるか?
+</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科登録表示ができる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>name: 'Java Spring'
+kana: 'Java Spring'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>name: 'WEB技術各論'
+kana: 'WEBぎじゅつかくろん'</t>
+    <rPh sb="9" eb="11">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクロン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科情報入力して、登録ボタンクリック</t>
+    <rPh sb="0" eb="2">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科詳細表示がでるか？</t>
+    <rPh sb="2" eb="4">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科詳細表示がでる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科情報入力して、登録ボタンクリック</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">教科登録表示へ(教科名重複エラー)
+教科詳細表示へ
+</t>
+    <rPh sb="0" eb="2">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>キョウカメイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジュウフク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科登録表示へ(教科名重複エラー)
+教科詳細表示へ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科登録表示(教科名重複エラー)がでるか？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科登録表示(教科名重複エラー)がでる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>urlを入力してアクセス(ログイン済み)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科更新表示機能</t>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>url: 'localhost:8080/manager/subject_update?id=4'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科情報入力して、更新ボタンクリック</t>
+    <rPh sb="0" eb="2">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>name: 'Python'
+kana: 'Python'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">教科更新表示へ(教科名重複エラー)
+教科詳細表示へ
+</t>
+    <rPh sb="0" eb="2">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>キョウカメイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジュウフク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科情報入力して、更新ボタンクリック</t>
+    <rPh sb="9" eb="11">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科更新表示へ(教科名重複エラー)
+教科詳細表示へ</t>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科更新表示(教科名重複エラー)がでるか？</t>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科更新表示(教科名重複エラー)がでる</t>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻登録表示機能</t>
+    <rPh sb="0" eb="2">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻更新表示機能</t>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻情報入力して、登録ボタンクリック</t>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻情報入力して、登録ボタンクリック</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>url: 'localhost:8080/manager/major_register'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ログイン表示へ
+専攻登録表示へ</t>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ログイン表示へ
+専攻登録表示へ</t>
+    <rPh sb="12" eb="14">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+専攻登録表示ができるか?
+</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻登録表示ができる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">専攻登録表示へ(専攻名重複エラー)
+専攻詳細表示へ
+</t>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジュウフク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻詳細表示がでるか？</t>
+    <rPh sb="2" eb="4">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻登録表示(専攻名重複エラー)がでるか？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻登録表示へ(専攻名重複エラー)
+専攻詳細表示へ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻詳細表示がでる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻登録表示(教科名重複エラー)がでる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ログイン表示へ
+専攻更新表示へ</t>
+    <rPh sb="10" eb="12">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ログイン表示へ
+専攻更新表示へ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻詳細表示がでる</t>
+    <rPh sb="0" eb="2">
+      <t>センコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻情報入力して、更新ボタンクリック</t>
+    <rPh sb="0" eb="2">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻情報入力して、更新ボタンクリック</t>
+    <rPh sb="0" eb="2">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻更新表示(専攻名重複エラー)がでる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>name: 'ITプログラマー'
+kana: 'ITプログラマー'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>name: 'UI/UX'
+kana: 'UI/UX'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>url: 'localhost:8080/manager/major_update?id=4'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>name: 'ホワイトハッカー'
+kana: 'ホワイトハッカー'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">専攻更新表示へ(専攻名重複エラー)
+専攻詳細表示へ
+</t>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジュウフク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻更新表示へ(専攻名重複エラー)
+専攻詳細表示へ</t>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス更新表示機能</t>
+    <rPh sb="3" eb="5">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス登録表示機能</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>url: 'localhost:8080/manager/class_register'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ログイン表示へ
+クラス登録表示へ</t>
+    <rPh sb="13" eb="15">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ログイン表示へ
+クラス登録表示へ</t>
+    <rPh sb="12" eb="14">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+クラス登録表示ができるか?
+</t>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>start_year: '2025'
+major_name: 'ホワイトハッカー'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス情報入力して、登録ボタンクリック</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>start_year: '2025'
+major_name: 'UIUX'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス詳細表示がでるか？</t>
+    <rPh sb="3" eb="5">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス詳細表示がでる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス登録表示(クラス重複エラー)がでる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス登録表示(クラス重複エラー)がでるか？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">クラス登録表示へ(クラス重複エラー)
+クラス詳細表示へ
+</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジュウフク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ログイン表示へ
+クラス更新表示へ</t>
+    <rPh sb="13" eb="15">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス情報入力して、登録ボタンクリック</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>url: 'localhost:8080/manager/class_update?id=4'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ログイン表示へ
+クラス更新表示へ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ログイン表示がでるか?</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ログイン表示がでる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>start_year: '2025'
+major_name: 'ITプログラマー'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス情報入力して、更新ボタンクリック</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス情報入力して、更新ボタンクリック</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">クラス更新表示へ(クラス重複エラー)
+クラス詳細表示へ
+</t>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジュウフク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス更新表示(クラス重複エラー)がでるか？</t>
+    <rPh sb="3" eb="5">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス詳細表示がでる</t>
+    <rPh sb="3" eb="5">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス更新表示(クラス重複エラー)がでる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス登録表示機能
+クラス更新表示機能
+共通</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キョウツウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス入力情報下、教科選択画面で複数教科選択</t>
+    <rPh sb="3" eb="7">
+      <t>ニュウリョクジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>センタクガメン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>省略</t>
+    <rPh sb="0" eb="1">
+      <t>ショウリャク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>既に選んでいる教科が、選択不可になっているか？</t>
+    <rPh sb="0" eb="1">
+      <t>スデ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>エラ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>既に選んでいる教科が、選択不可になっている</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クラス更新表示ができる
+既存値が入力の初期値になっている</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+クラス更新表示ができるか?
+既存値が入力の初期値になっているか？
+</t>
+    <rPh sb="16" eb="18">
+      <t>キソン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ショキチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+ログイン表示へ
+教科更新表示へ</t>
+    <rPh sb="12" eb="14">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ログイン表示へ
+教科更新表示へ</t>
+    <rPh sb="11" eb="13">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+教科更新表示ができるか?
+既存値が入力の初期値になっているか？
+</t>
+    <rPh sb="3" eb="5">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科更新表示ができる
+既存値が入力の初期値になっている</t>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻更新表示ができる
+既存値が入力の初期値になっている</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+専攻更新表示ができるか?
+既存値が入力の初期値になっているか？
+</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻更新表示(専攻名重複エラー)がでるか？</t>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>登録or更新ボタン、クリック後</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ゴ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>処理結果がポップアップされるか？</t>
+    <rPh sb="0" eb="4">
+      <t>ショリケッカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>処理結果がポップアップされる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>専攻登録表示機能
+専攻更新表示機能
+共通</t>
+    <rPh sb="9" eb="11">
+      <t>センコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>教科登録表示機能
+教科更新表示機能
+共通</t>
+    <rPh sb="0" eb="2">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>url: 'localhost:8080/manager/subject?id=4' (対象idパラメーターつき)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>url: 'localhost:8080/manager/subjects'</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -518,8 +1403,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -532,8 +1432,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -617,11 +1523,72 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -668,10 +1635,83 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -700,7 +1740,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -996,8 +2036,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE061E5-E733-47BF-AB92-A3BA53C205AF}">
-  <dimension ref="B3:I17"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="B4:I28"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="52.75" customWidth="1"/>
@@ -1008,8 +2048,7 @@
     <col min="8" max="8" width="48.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" ht="13.5"/>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B4" s="9" t="s">
         <v>0</v>
       </c>
@@ -1035,8 +2074,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="45.75">
-      <c r="B5" s="17" t="s">
+    <row r="5" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B5" s="35" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -1061,8 +2100,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="45.75">
-      <c r="B6" s="17"/>
+    <row r="6" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B6" s="35"/>
       <c r="C6" s="8" t="s">
         <v>16</v>
       </c>
@@ -1085,8 +2124,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="112.5" customHeight="1">
-      <c r="B7" s="17"/>
+    <row r="7" spans="2:9" ht="112.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="35"/>
       <c r="C7" s="8" t="s">
         <v>19</v>
       </c>
@@ -1103,8 +2142,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="111" customHeight="1">
-      <c r="B8" s="17"/>
+    <row r="8" spans="2:9" ht="111" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="35"/>
       <c r="C8" s="13" t="s">
         <v>22</v>
       </c>
@@ -1123,8 +2162,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="111.75" customHeight="1">
-      <c r="B9" s="18"/>
+    <row r="9" spans="2:9" ht="111.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="36"/>
       <c r="C9" s="8" t="s">
         <v>24</v>
       </c>
@@ -1143,45 +2182,45 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="118.5" customHeight="1">
-      <c r="B10" s="17" t="s">
-        <v>26</v>
+    <row r="10" spans="2:9" ht="118.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="37" t="s">
+        <v>114</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="I10" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="45.75">
-      <c r="B11" s="17"/>
+    <row r="11" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B11" s="35"/>
       <c r="C11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>17</v>
@@ -1193,48 +2232,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="76.5">
-      <c r="B12" s="17"/>
+    <row r="12" spans="2:9" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="B12" s="35"/>
       <c r="C12" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="11"/>
       <c r="F12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="168.75" x14ac:dyDescent="0.4">
+      <c r="B13" s="35"/>
+      <c r="C13" s="13" t="s">
         <v>35</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" ht="137.25">
-      <c r="B13" s="17"/>
-      <c r="C13" s="13" t="s">
-        <v>36</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="H13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="15" t="s">
-        <v>39</v>
-      </c>
       <c r="I13" s="16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="213">
-      <c r="B14" s="17"/>
+    <row r="14" spans="2:9" ht="262.5" x14ac:dyDescent="0.4">
+      <c r="B14" s="35"/>
       <c r="C14" s="8" t="s">
         <v>19</v>
       </c>
@@ -1253,8 +2292,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="213">
-      <c r="B15" s="17"/>
+    <row r="15" spans="2:9" ht="262.5" x14ac:dyDescent="0.4">
+      <c r="B15" s="35"/>
       <c r="C15" s="13" t="s">
         <v>22</v>
       </c>
@@ -1273,8 +2312,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="106.5">
-      <c r="B16" s="17"/>
+    <row r="16" spans="2:9" ht="131.25" x14ac:dyDescent="0.4">
+      <c r="B16" s="35"/>
       <c r="C16" s="8" t="s">
         <v>24</v>
       </c>
@@ -1293,39 +2332,259 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="30.75">
-      <c r="B17" s="17"/>
+    <row r="17" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B17" s="35"/>
       <c r="C17" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="I17" s="2" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="18" spans="2:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="B18" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B19" s="39"/>
+      <c r="C19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="B20" s="39"/>
+      <c r="C20" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B21" s="40"/>
+      <c r="C21" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="B22" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="E22" s="23"/>
+      <c r="F22" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B23" s="42"/>
+      <c r="C23" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="E23" s="23"/>
+      <c r="F23" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="B24" s="42"/>
+      <c r="C24" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B25" s="42"/>
+      <c r="C25" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B26" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="E26" s="23"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="I26" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B27" s="34"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B28" s="34"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B5:B9"/>
     <mergeCell ref="B10:B17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B22:B25"/>
   </mergeCells>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFCB6322-B210-45C8-B36D-ABAABAFDD3E1}">
-  <dimension ref="B3:I17"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="B4:I26"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="52.75" customWidth="1"/>
@@ -1336,8 +2595,7 @@
     <col min="8" max="8" width="48.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" ht="13.5"/>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B4" s="9" t="s">
         <v>0</v>
       </c>
@@ -1363,45 +2621,45 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="45.75">
-      <c r="B5" s="17" t="s">
-        <v>44</v>
+    <row r="5" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B5" s="35" t="s">
+        <v>43</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>45</v>
+        <v>217</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="I5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="45.75">
-      <c r="B6" s="17"/>
+    <row r="6" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B6" s="35"/>
       <c r="C6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>17</v>
@@ -1413,8 +2671,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="112.5" customHeight="1">
-      <c r="B7" s="17"/>
+    <row r="7" spans="2:9" ht="112.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="35"/>
       <c r="C7" s="8" t="s">
         <v>19</v>
       </c>
@@ -1433,8 +2691,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="111" customHeight="1">
-      <c r="B8" s="17"/>
+    <row r="8" spans="2:9" ht="111" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="35"/>
       <c r="C8" s="13" t="s">
         <v>22</v>
       </c>
@@ -1453,8 +2711,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="111.75" customHeight="1">
-      <c r="B9" s="18"/>
+    <row r="9" spans="2:9" ht="111.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="36"/>
       <c r="C9" s="8" t="s">
         <v>24</v>
       </c>
@@ -1473,45 +2731,45 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="118.5" customHeight="1">
-      <c r="B10" s="17" t="s">
-        <v>49</v>
+    <row r="10" spans="2:9" ht="118.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="37" t="s">
+        <v>115</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>50</v>
+        <v>216</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="45.75">
-      <c r="B11" s="17"/>
+    <row r="11" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B11" s="35"/>
       <c r="C11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>50</v>
+        <v>216</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>17</v>
@@ -1523,48 +2781,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="76.5">
-      <c r="B12" s="17"/>
+    <row r="12" spans="2:9" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="B12" s="35"/>
       <c r="C12" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="11"/>
       <c r="F12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="168.75" x14ac:dyDescent="0.4">
+      <c r="B13" s="35"/>
+      <c r="C13" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" ht="137.25">
-      <c r="B13" s="17"/>
-      <c r="C13" s="13" t="s">
-        <v>59</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I13" s="16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="213">
-      <c r="B14" s="17"/>
+    <row r="14" spans="2:9" ht="262.5" x14ac:dyDescent="0.4">
+      <c r="B14" s="35"/>
       <c r="C14" s="8" t="s">
         <v>19</v>
       </c>
@@ -1583,8 +2841,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="213">
-      <c r="B15" s="17"/>
+    <row r="15" spans="2:9" ht="262.5" x14ac:dyDescent="0.4">
+      <c r="B15" s="35"/>
       <c r="C15" s="13" t="s">
         <v>22</v>
       </c>
@@ -1603,8 +2861,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="106.5">
-      <c r="B16" s="17"/>
+    <row r="16" spans="2:9" ht="131.25" x14ac:dyDescent="0.4">
+      <c r="B16" s="35"/>
       <c r="C16" s="8" t="s">
         <v>24</v>
       </c>
@@ -1623,39 +2881,253 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="30.75">
-      <c r="B17" s="17"/>
+    <row r="17" spans="2:9" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B17" s="35"/>
       <c r="C17" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="18" spans="2:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="B18" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B19" s="39"/>
+      <c r="C19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="B20" s="39"/>
+      <c r="C20" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B21" s="40"/>
+      <c r="C21" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="B22" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="23"/>
+      <c r="F22" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B23" s="42"/>
+      <c r="C23" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E23" s="23"/>
+      <c r="F23" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="B24" s="42"/>
+      <c r="C24" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B25" s="42"/>
+      <c r="C25" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B26" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="E26" s="23"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="I26" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B5:B9"/>
     <mergeCell ref="B10:B17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B22:B25"/>
   </mergeCells>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C240EB-C576-4E36-B120-365E70A5971C}">
-  <dimension ref="B3:I17"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="B4:I30"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="52.75" customWidth="1"/>
@@ -1666,8 +3138,7 @@
     <col min="8" max="8" width="48.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" ht="13.5"/>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B4" s="9" t="s">
         <v>0</v>
       </c>
@@ -1693,45 +3164,45 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="60.75">
-      <c r="B5" s="17" t="s">
-        <v>67</v>
+    <row r="5" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B5" s="35" t="s">
+        <v>64</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="45.75">
-      <c r="B6" s="17"/>
+    <row r="6" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B6" s="35"/>
       <c r="C6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>17</v>
@@ -1743,8 +3214,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="112.5" customHeight="1">
-      <c r="B7" s="17"/>
+    <row r="7" spans="2:9" ht="112.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="35"/>
       <c r="C7" s="8" t="s">
         <v>19</v>
       </c>
@@ -1763,8 +3234,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="111" customHeight="1">
-      <c r="B8" s="17"/>
+    <row r="8" spans="2:9" ht="111" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="35"/>
       <c r="C8" s="13" t="s">
         <v>22</v>
       </c>
@@ -1783,8 +3254,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="111.75" customHeight="1">
-      <c r="B9" s="18"/>
+    <row r="9" spans="2:9" ht="111.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="36"/>
       <c r="C9" s="8" t="s">
         <v>24</v>
       </c>
@@ -1803,45 +3274,45 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="118.5" customHeight="1">
-      <c r="B10" s="17" t="s">
-        <v>72</v>
+    <row r="10" spans="2:9" ht="118.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="37" t="s">
+        <v>116</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="45.75">
-      <c r="B11" s="17"/>
+    <row r="11" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B11" s="35"/>
       <c r="C11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>17</v>
@@ -1853,48 +3324,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="76.5">
-      <c r="B12" s="17"/>
+    <row r="12" spans="2:9" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="B12" s="35"/>
       <c r="C12" s="8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="11"/>
       <c r="F12" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="137.25">
-      <c r="B13" s="17"/>
+    <row r="13" spans="2:9" ht="168.75" x14ac:dyDescent="0.4">
+      <c r="B13" s="35"/>
       <c r="C13" s="13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="15" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I13" s="16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="213">
-      <c r="B14" s="17"/>
+    <row r="14" spans="2:9" ht="262.5" x14ac:dyDescent="0.4">
+      <c r="B14" s="35"/>
       <c r="C14" s="8" t="s">
         <v>19</v>
       </c>
@@ -1913,8 +3384,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="213">
-      <c r="B15" s="17"/>
+    <row r="15" spans="2:9" ht="262.5" x14ac:dyDescent="0.4">
+      <c r="B15" s="35"/>
       <c r="C15" s="13" t="s">
         <v>22</v>
       </c>
@@ -1933,8 +3404,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="106.5">
-      <c r="B16" s="17"/>
+    <row r="16" spans="2:9" ht="131.25" x14ac:dyDescent="0.4">
+      <c r="B16" s="35"/>
       <c r="C16" s="8" t="s">
         <v>24</v>
       </c>
@@ -1953,39 +3424,303 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="45.75">
-      <c r="B17" s="17"/>
+    <row r="17" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B17" s="35"/>
       <c r="C17" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="18" spans="2:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="B18" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B19" s="39"/>
+      <c r="C19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="B20" s="39"/>
+      <c r="C20" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="B21" s="40"/>
+      <c r="C21" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="B22" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="E22" s="23"/>
+      <c r="F22" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B23" s="42"/>
+      <c r="C23" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="E23" s="23"/>
+      <c r="F23" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="B24" s="42"/>
+      <c r="C24" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="B25" s="42"/>
+      <c r="C25" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="F25" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="H25" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="E26" s="23"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="I26" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B27" s="43"/>
+      <c r="C27" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="E27" s="23"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="H27" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="I27" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B28" s="30"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B29" s="30"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
+    <mergeCell ref="B26:B27"/>
     <mergeCell ref="B5:B9"/>
     <mergeCell ref="B10:B17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B22:B25"/>
   </mergeCells>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BD68364-44F4-4C01-AA1F-DAB8E208C776}">
-  <dimension ref="B3:I11"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="B4:I11"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="52.75" customWidth="1"/>
@@ -1996,8 +3731,7 @@
     <col min="8" max="8" width="42.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" ht="13.5"/>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B4" s="9" t="s">
         <v>0</v>
       </c>
@@ -2023,45 +3757,45 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="106.5">
-      <c r="B5" s="18" t="s">
-        <v>89</v>
+    <row r="5" spans="2:9" ht="131.25" x14ac:dyDescent="0.4">
+      <c r="B5" s="36" t="s">
+        <v>85</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="I5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="106.5">
-      <c r="B6" s="19"/>
+    <row r="6" spans="2:9" ht="131.25" x14ac:dyDescent="0.4">
+      <c r="B6" s="44"/>
       <c r="C6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>17</v>
@@ -2073,8 +3807,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="112.5" customHeight="1">
-      <c r="B7" s="19"/>
+    <row r="7" spans="2:9" ht="112.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="44"/>
       <c r="C7" s="8" t="s">
         <v>19</v>
       </c>
@@ -2093,8 +3827,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="111" customHeight="1">
-      <c r="B8" s="19"/>
+    <row r="8" spans="2:9" ht="111" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="44"/>
       <c r="C8" s="13" t="s">
         <v>22</v>
       </c>
@@ -2113,8 +3847,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="111.75" customHeight="1">
-      <c r="B9" s="20"/>
+    <row r="9" spans="2:9" ht="111.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="45"/>
       <c r="C9" s="2" t="s">
         <v>24</v>
       </c>
@@ -2133,7 +3867,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="118.5" customHeight="1">
+    <row r="10" spans="2:9" ht="118.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="12"/>
       <c r="C10" s="5"/>
       <c r="D10" s="6"/>
@@ -2143,7 +3877,7 @@
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
-    <row r="11" spans="2:9">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C11" s="5"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -2156,14 +3890,15 @@
   <mergeCells count="1">
     <mergeCell ref="B5:B9"/>
   </mergeCells>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B4:I13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="B4:I12"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
     <col min="3" max="3" width="52.75" customWidth="1"/>
@@ -2174,7 +3909,7 @@
     <col min="8" max="8" width="42.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:9" ht="15.75">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B4" s="9" t="s">
         <v>0</v>
       </c>
@@ -2200,188 +3935,188 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="137.25">
-      <c r="B5" s="21" t="s">
+    <row r="5" spans="2:9" ht="168.75" x14ac:dyDescent="0.4">
+      <c r="B5" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="G5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="I5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="168.75" x14ac:dyDescent="0.4">
+      <c r="B6" s="46"/>
+      <c r="C6" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="E6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I6" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="112.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="46"/>
+      <c r="C7" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" ht="137.25">
-      <c r="B6" s="21"/>
-      <c r="C6" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I7" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="111" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="46"/>
+      <c r="C8" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="112.5" customHeight="1">
-      <c r="B7" s="21"/>
-      <c r="C7" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="111.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="46"/>
+      <c r="C9" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="E9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="118.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="46"/>
+      <c r="C10" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="E10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="111" customHeight="1">
-      <c r="B8" s="21"/>
-      <c r="C8" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="H10" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="111.75" customHeight="1">
-      <c r="B9" s="21"/>
-      <c r="C9" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="I10" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="108" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="46"/>
+      <c r="C11" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" ht="118.5" customHeight="1">
-      <c r="B10" s="21"/>
-      <c r="C10" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="108" customHeight="1">
-      <c r="B11" s="21"/>
-      <c r="C11" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="I11" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="108" customHeight="1">
-      <c r="B12" s="21"/>
+    <row r="12" spans="2:9" ht="108" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="46"/>
       <c r="C12" s="8" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>18</v>
@@ -2390,11 +4125,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="15.75"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B5:B12"/>
   </mergeCells>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/成績管理sys_テスト仕様書.xlsx
+++ b/成績管理sys_テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri_sys\seiseki_manage_sys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F5B7AC-99FE-494E-8752-88B71F8BE144}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF996002-1ECE-446B-8D98-4E86BC472911}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="専攻情報管理機能" sheetId="5" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="218">
   <si>
     <t>機能名</t>
   </si>
@@ -659,10 +659,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>url: 'localhost:8080/manager/subject_update?id=4'</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>教科情報入力して、更新ボタンクリック</t>
     <rPh sb="0" eb="2">
       <t>キョウカ</t>
@@ -923,10 +919,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>url: 'localhost:8080/manager/major_update?id=4'</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>name: 'ホワイトハッカー'
 kana: 'ホワイトハッカー'</t>
     <phoneticPr fontId="2"/>
@@ -1081,10 +1073,6 @@
   </si>
   <si>
     <t>クラス情報入力して、登録ボタンクリック</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>url: 'localhost:8080/manager/class_update?id=4'</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1381,6 +1369,18 @@
   </si>
   <si>
     <t>url: 'localhost:8080/manager/subjects'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>url: 'localhost:8080/manager/major_update?id=10'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>url: 'localhost:8080/manager/subject_update?id=34'</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>url: 'localhost:8080/manager/class_update?id=17'</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2354,23 +2354,23 @@
     </row>
     <row r="18" spans="2:9" ht="75" x14ac:dyDescent="0.4">
       <c r="B18" s="38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="I18" s="17" t="s">
         <v>15</v>
@@ -2382,11 +2382,11 @@
         <v>16</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>17</v>
@@ -2401,22 +2401,22 @@
     <row r="20" spans="2:9" ht="75" x14ac:dyDescent="0.4">
       <c r="B20" s="39"/>
       <c r="C20" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F20" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="H20" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I20" s="17" t="s">
         <v>15</v>
@@ -2425,22 +2425,22 @@
     <row r="21" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
       <c r="B21" s="40"/>
       <c r="C21" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I21" s="16" t="s">
         <v>15</v>
@@ -2448,23 +2448,25 @@
     </row>
     <row r="22" spans="2:9" ht="93.75" x14ac:dyDescent="0.4">
       <c r="B22" s="41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>133</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" s="23"/>
+        <v>215</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>164</v>
+      </c>
       <c r="F22" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I22" s="21" t="s">
         <v>15</v>
@@ -2476,11 +2478,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="E23" s="23"/>
+        <v>215</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>164</v>
+      </c>
       <c r="F23" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G23" s="24" t="s">
         <v>17</v>
@@ -2495,22 +2499,22 @@
     <row r="24" spans="2:9" ht="75" x14ac:dyDescent="0.4">
       <c r="B24" s="42"/>
       <c r="C24" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D24" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E24" s="25" t="s">
-        <v>165</v>
-      </c>
       <c r="F24" s="24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I24" s="21" t="s">
         <v>15</v>
@@ -2519,22 +2523,22 @@
     <row r="25" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
       <c r="B25" s="42"/>
       <c r="C25" s="21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D25" s="25" t="s">
         <v>165</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I25" s="21" t="s">
         <v>15</v>
@@ -2542,21 +2546,21 @@
     </row>
     <row r="26" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
       <c r="B26" s="32" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E26" s="23"/>
       <c r="F26" s="26"/>
       <c r="G26" s="24" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I26" s="21" t="s">
         <v>15</v>
@@ -2629,7 +2633,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>11</v>
@@ -2739,7 +2743,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
@@ -2763,7 +2767,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>11</v>
@@ -3003,17 +3007,19 @@
         <v>133</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22" s="23"/>
+        <v>216</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>123</v>
+      </c>
       <c r="F22" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="H22" s="24" t="s">
         <v>204</v>
-      </c>
-      <c r="G22" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="H22" s="24" t="s">
-        <v>207</v>
       </c>
       <c r="I22" s="21" t="s">
         <v>15</v>
@@ -3025,11 +3031,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="E23" s="23"/>
+        <v>216</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>123</v>
+      </c>
       <c r="F23" s="24" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G23" s="24" t="s">
         <v>17</v>
@@ -3044,16 +3052,16 @@
     <row r="24" spans="2:9" ht="75" x14ac:dyDescent="0.4">
       <c r="B24" s="42"/>
       <c r="C24" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="E24" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="24" t="s">
         <v>137</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>138</v>
       </c>
       <c r="G24" s="24" t="s">
         <v>126</v>
@@ -3068,22 +3076,22 @@
     <row r="25" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
       <c r="B25" s="42"/>
       <c r="C25" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="D25" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="E25" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="F25" s="24" t="s">
+      <c r="G25" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="G25" s="24" t="s">
+      <c r="H25" s="24" t="s">
         <v>141</v>
-      </c>
-      <c r="H25" s="24" t="s">
-        <v>142</v>
       </c>
       <c r="I25" s="21" t="s">
         <v>15</v>
@@ -3091,21 +3099,21 @@
     </row>
     <row r="26" spans="2:9" ht="56.25" x14ac:dyDescent="0.4">
       <c r="B26" s="32" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E26" s="23"/>
       <c r="F26" s="26"/>
       <c r="G26" s="24" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I26" s="21" t="s">
         <v>15</v>
@@ -3446,23 +3454,23 @@
     </row>
     <row r="18" spans="2:9" ht="75" x14ac:dyDescent="0.4">
       <c r="B18" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>175</v>
-      </c>
       <c r="H18" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I18" s="17" t="s">
         <v>15</v>
@@ -3474,11 +3482,11 @@
         <v>16</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>17</v>
@@ -3493,22 +3501,22 @@
     <row r="20" spans="2:9" ht="75" x14ac:dyDescent="0.4">
       <c r="B20" s="39"/>
       <c r="C20" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D20" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="E20" s="25" t="s">
+      <c r="H20" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="I20" s="17" t="s">
         <v>15</v>
@@ -3517,22 +3525,22 @@
     <row r="21" spans="2:9" ht="75" x14ac:dyDescent="0.4">
       <c r="B21" s="40"/>
       <c r="C21" s="13" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I21" s="16" t="s">
         <v>15</v>
@@ -3540,23 +3548,25 @@
     </row>
     <row r="22" spans="2:9" ht="93.75" x14ac:dyDescent="0.4">
       <c r="B22" s="41" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>133</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="E22" s="23"/>
+        <v>217</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>174</v>
+      </c>
       <c r="F22" s="24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I22" s="21" t="s">
         <v>15</v>
@@ -3568,17 +3578,19 @@
         <v>16</v>
       </c>
       <c r="D23" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="H23" s="21" t="s">
         <v>186</v>
-      </c>
-      <c r="E23" s="23"/>
-      <c r="F23" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="H23" s="21" t="s">
-        <v>189</v>
       </c>
       <c r="I23" s="21" t="s">
         <v>15</v>
@@ -3587,22 +3599,22 @@
     <row r="24" spans="2:9" ht="75" x14ac:dyDescent="0.4">
       <c r="B24" s="42"/>
       <c r="C24" s="21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D24" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="F24" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="E24" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>193</v>
-      </c>
       <c r="G24" s="24" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I24" s="21" t="s">
         <v>15</v>
@@ -3611,22 +3623,22 @@
     <row r="25" spans="2:9" ht="75" x14ac:dyDescent="0.4">
       <c r="B25" s="42"/>
       <c r="C25" s="28" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="E25" s="31" t="s">
         <v>176</v>
       </c>
+      <c r="E25" s="25" t="s">
+        <v>187</v>
+      </c>
       <c r="F25" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="H25" s="29" t="s">
         <v>193</v>
-      </c>
-      <c r="G25" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="H25" s="29" t="s">
-        <v>196</v>
       </c>
       <c r="I25" s="28" t="s">
         <v>15</v>
@@ -3634,21 +3646,21 @@
     </row>
     <row r="26" spans="2:9" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="43" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E26" s="23"/>
       <c r="F26" s="26"/>
       <c r="G26" s="24" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I26" s="21" t="s">
         <v>15</v>
@@ -3657,18 +3669,18 @@
     <row r="27" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B27" s="43"/>
       <c r="C27" s="21" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E27" s="23"/>
       <c r="F27" s="26"/>
       <c r="G27" s="24" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I27" s="21" t="s">
         <v>15</v>
